--- a/Horario desenvolvido/Relatorio_Tempos_Cedidos_Proposta_3.xlsx
+++ b/Horario desenvolvido/Relatorio_Tempos_Cedidos_Proposta_3.xlsx
@@ -1603,10 +1603,10 @@
         <v>68</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>0.08823529411764706</v>
+        <v>0.1029411764705882</v>
       </c>
     </row>
     <row r="4">
@@ -1636,12 +1636,12 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Ed.Física</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
@@ -1651,21 +1651,21 @@
         <v>28</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>0.1071428571428571</v>
+        <v>0.07142857142857142</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Ed.Física</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C6" s="6" t="n">
@@ -2214,69 +2214,69 @@
         <v>68</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>0.08823529411764706</v>
+        <v>0.1029411764705882</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>MFo (Mário Henrique Fonseca)</t>
         </is>
       </c>
       <c r="C4" s="6" t="n">
         <v>2</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E4" s="6" t="n">
         <v>3</v>
       </c>
       <c r="F4" s="8" t="n">
-        <v>0.1071428571428571</v>
+        <v>0.1153846153846154</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Ed.Física</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>MFo (Mário Henrique Fonseca)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
         <v>2</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>0.1153846153846154</v>
+        <v>0.07142857142857142</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Ed.Física</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C6" s="6" t="n">

--- a/Horario desenvolvido/Relatorio_Tempos_Cedidos_Proposta_3.xlsx
+++ b/Horario desenvolvido/Relatorio_Tempos_Cedidos_Proposta_3.xlsx
@@ -1603,10 +1603,10 @@
         <v>68</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>0.08823529411764706</v>
+        <v>0.1029411764705882</v>
       </c>
     </row>
     <row r="4">
@@ -1636,12 +1636,12 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Ed.Física</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
@@ -1651,21 +1651,21 @@
         <v>28</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>0.1071428571428571</v>
+        <v>0.07142857142857142</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Ed.Física</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C6" s="6" t="n">
@@ -2214,69 +2214,69 @@
         <v>68</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>0.08823529411764706</v>
+        <v>0.1029411764705882</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>MFo (Mário Henrique Fonseca)</t>
         </is>
       </c>
       <c r="C4" s="6" t="n">
         <v>2</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E4" s="6" t="n">
         <v>3</v>
       </c>
       <c r="F4" s="8" t="n">
-        <v>0.1071428571428571</v>
+        <v>0.1153846153846154</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Ed.Física</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>MFo (Mário Henrique Fonseca)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
         <v>2</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>0.1153846153846154</v>
+        <v>0.07142857142857142</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Ed.Física</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C6" s="6" t="n">
@@ -3951,10 +3951,10 @@
         <v>56</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>0.07142857142857142</v>
+        <v>0.08928571428571429</v>
       </c>
     </row>
     <row r="4">
@@ -4176,36 +4176,36 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Proj.Vestibular</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>108</v>
+        <v>28</v>
       </c>
       <c r="E13" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>0.009259259259259259</v>
+        <v>0.03571428571428571</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Ed.Física</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Fab (Fabio Merçon)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C14" s="6" t="n">
@@ -4215,28 +4215,28 @@
         <v>28</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>0.03571428571428571</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Ed.Física</t>
+          <t>Fil</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="E15" s="3" t="n">
         <v>0</v>
@@ -4248,19 +4248,19 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Fil</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C16" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D16" s="6" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="E16" s="6" t="n">
         <v>0</v>
@@ -4272,19 +4272,19 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>0</v>
@@ -4296,19 +4296,19 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Wag (Wagner Pinto da Silva)</t>
+          <t>Bre (Carlos Luiz Silva Brener)</t>
         </is>
       </c>
       <c r="C18" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D18" s="6" t="n">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="E18" s="6" t="n">
         <v>0</v>
@@ -4320,19 +4320,19 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Proj.Vestibular</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Bre (Carlos Luiz Silva Brener)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>28</v>
+        <v>108</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>0</v>
@@ -4475,49 +4475,49 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>Isb (Isabela Gomes Bustamante)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C3" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="E3" s="3" t="n">
         <v>5</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>0.131578947368421</v>
+        <v>0.08928571428571429</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Isb (Isabela Gomes Bustamante)</t>
         </is>
       </c>
       <c r="C4" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F4" s="8" t="n">
-        <v>0.07142857142857142</v>
+        <v>0.131578947368421</v>
       </c>
     </row>
     <row r="5">
@@ -4715,7 +4715,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Proj.Vestibular</t>
+          <t>Ed.Física</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
@@ -4724,34 +4724,34 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>108</v>
+        <v>28</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>0.009259259259259259</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Ed.Física</t>
+          <t>Fil</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="E14" s="6" t="n">
         <v>0</v>
@@ -4763,19 +4763,19 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Fil</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="E15" s="3" t="n">
         <v>0</v>
@@ -4787,19 +4787,19 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Bre (Carlos Luiz Silva Brener)</t>
         </is>
       </c>
       <c r="C16" s="6" t="n">
         <v>2</v>
       </c>
       <c r="D16" s="6" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E16" s="6" t="n">
         <v>0</v>
@@ -4811,19 +4811,19 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Proj.Vestibular</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Bre (Carlos Luiz Silva Brener)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>26</v>
+        <v>108</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>0</v>

--- a/Horario desenvolvido/Relatorio_Tempos_Cedidos_Proposta_3.xlsx
+++ b/Horario desenvolvido/Relatorio_Tempos_Cedidos_Proposta_3.xlsx
@@ -645,10 +645,10 @@
         <v>32</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>0.09375</v>
+        <v>0.0625</v>
       </c>
     </row>
     <row r="7">
@@ -678,49 +678,49 @@
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
         </is>
       </c>
       <c r="C8" s="6" t="n">
         <v>2</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>0.03333333333333333</v>
+        <v>0.0625</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C9" s="3" t="n">
         <v>2</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E9" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>0.03125</v>
+        <v>0.03333333333333333</v>
       </c>
     </row>
     <row r="10">
@@ -1136,10 +1136,10 @@
         <v>32</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>0.09375</v>
+        <v>0.0625</v>
       </c>
     </row>
     <row r="6">
@@ -1217,25 +1217,25 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="E9" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>0.02222222222222222</v>
+        <v>0.03333333333333333</v>
       </c>
     </row>
     <row r="10">
@@ -1385,19 +1385,19 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
+          <t>APa (Ana Patricia Machado de Pinho Garcia), PaH (Paulo Henrique Sá Júnior), Velo (Rodrigo Veloso)</t>
         </is>
       </c>
       <c r="C16" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D16" s="6" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="E16" s="6" t="n">
         <v>0</v>
@@ -1409,19 +1409,19 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>APa (Ana Patricia Machado de Pinho Garcia), PaH (Paulo Henrique Sá Júnior), Velo (Rodrigo Veloso)</t>
+          <t>Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>60</v>
+        <v>16</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>0</v>
@@ -1433,19 +1433,19 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Fab (Fabio Merçon)</t>
+          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C18" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D18" s="6" t="n">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="E18" s="6" t="n">
         <v>0</v>
@@ -1514,10 +1514,10 @@
         <v>617</v>
       </c>
       <c r="E21" s="9" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>0.02917341977309562</v>
+        <v>0.02755267423014587</v>
       </c>
     </row>
   </sheetData>

--- a/Horario desenvolvido/Relatorio_Tempos_Cedidos_Proposta_3.xlsx
+++ b/Horario desenvolvido/Relatorio_Tempos_Cedidos_Proposta_3.xlsx
@@ -1612,36 +1612,36 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Ed.Física</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>APa (Ana Patricia Machado de Pinho Garcia)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C4" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>54</v>
+        <v>28</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F4" s="8" t="n">
-        <v>0.09259259259259259</v>
+        <v>0.07142857142857142</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Ed.Física</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
@@ -1660,12 +1660,12 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
         </is>
       </c>
       <c r="C6" s="6" t="n">
@@ -1684,25 +1684,25 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
+          <t>APa (Ana Patricia Machado de Pinho Garcia)</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>28</v>
+        <v>54</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>2</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>0.07142857142857142</v>
+        <v>0.03703703703703703</v>
       </c>
     </row>
     <row r="8">
@@ -1756,25 +1756,25 @@
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>VSi (Vinícius de Paula Silveira)</t>
+          <t>Lza (Luiza Maria Abreu de Mattos)</t>
         </is>
       </c>
       <c r="C10" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="E10" s="6" t="n">
         <v>1</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>0.03846153846153846</v>
+        <v>0.025</v>
       </c>
     </row>
     <row r="11">
@@ -1900,19 +1900,19 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Eletiva</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Lza (Luiza Maria Abreu de Mattos)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C16" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D16" s="6" t="n">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="E16" s="6" t="n">
         <v>0</v>
@@ -1924,12 +1924,12 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Eletiva</t>
+          <t>Fil</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C17" s="3" t="n">
@@ -1948,12 +1948,12 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Fil</t>
+          <t>Finanças</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>Mlo (Marcelo Rios Lopes)</t>
         </is>
       </c>
       <c r="C18" s="6" t="n">
@@ -1972,19 +1972,19 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Finanças</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Mlo (Marcelo Rios Lopes)</t>
+          <t>VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>0</v>
@@ -2125,10 +2125,10 @@
         <v>598</v>
       </c>
       <c r="E25" s="9" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>0.04347826086956522</v>
+        <v>0.03846153846153846</v>
       </c>
     </row>
   </sheetData>
@@ -2214,10 +2214,10 @@
         <v>68</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>0.1029411764705882</v>
+        <v>0.08823529411764706</v>
       </c>
     </row>
     <row r="4">
@@ -2238,10 +2238,10 @@
         <v>26</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F4" s="8" t="n">
-        <v>0.1153846153846154</v>
+        <v>0.1538461538461539</v>
       </c>
     </row>
     <row r="5">
@@ -2319,25 +2319,25 @@
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Vir (Virgínia Granadeiro Chaves Silva)</t>
+          <t>BrSa (Bruno Vianna dos Santos)</t>
         </is>
       </c>
       <c r="C8" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>56</v>
+        <v>42</v>
       </c>
       <c r="E8" s="6" t="n">
         <v>2</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>0.03571428571428571</v>
+        <v>0.04761904761904762</v>
       </c>
     </row>
     <row r="9">
@@ -2348,92 +2348,92 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>BrSa (Bruno Vianna dos Santos)</t>
+          <t>FBri (Fábio Luís de Brito)</t>
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="E9" s="3" t="n">
         <v>2</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>0.04761904761904762</v>
+        <v>0.07692307692307693</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Artes</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>FBri (Fábio Luís de Brito)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C10" s="6" t="n">
         <v>2</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.03571428571428571</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Artes</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Lza (Luiza Maria Abreu de Mattos)</t>
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="E11" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>0.03571428571428571</v>
+        <v>0.025</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Lza (Luiza Maria Abreu de Mattos)</t>
+          <t>Vir (Virgínia Granadeiro Chaves Silva)</t>
         </is>
       </c>
       <c r="C12" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="E12" s="6" t="n">
         <v>1</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>0.025</v>
+        <v>0.01785714285714286</v>
       </c>
     </row>
     <row r="13">
@@ -2736,10 +2736,10 @@
         <v>598</v>
       </c>
       <c r="E25" s="9" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>0.04180602006688963</v>
+        <v>0.04013377926421405</v>
       </c>
     </row>
   </sheetData>
